--- a/fondo_pensione.xlsx
+++ b/fondo_pensione.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sportland-my.sharepoint.com/personal/michele_manfrin_3asport_it/Documents/Desktop/Michele/Privata/Banca/Investimenti/Pilastro 5 - Il Fondo Pensione/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luca.arietti\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1738" documentId="8_{070FC835-0ED3-404F-AFB5-2D620460021C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{649B7A2B-FD02-455F-8CF0-8CC50B0D811A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B8A72B0-2446-46C8-9009-D4E9D274436B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{45DD0601-7E0B-41B3-A9BC-2726C91B7179}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{45DD0601-7E0B-41B3-A9BC-2726C91B7179}"/>
   </bookViews>
   <sheets>
     <sheet name="Fondo Pensione Fineco Amundi" sheetId="1" r:id="rId1"/>
@@ -487,6 +487,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="9" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="2" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="9" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -505,22 +521,6 @@
     <xf numFmtId="164" fontId="2" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="9" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="2" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="9" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Migliaia" xfId="1" builtinId="3"/>
@@ -859,21 +859,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1821D431-B7C0-4240-9745-B48D527EFB38}">
   <dimension ref="A1:AV55"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="55.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="55.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="15" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="42" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="43" max="47" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="15" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="42" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="43" max="47" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:48" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -1016,7 +1016,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="2" spans="1:48" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
         <v>23</v>
       </c>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="AV2" s="8"/>
     </row>
-    <row r="3" spans="1:48" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
         <v>21</v>
       </c>
@@ -1395,7 +1395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:48" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
         <v>2</v>
       </c>
@@ -1584,7 +1584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:48" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
         <v>15</v>
       </c>
@@ -1773,385 +1773,385 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:48" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
         <v>16</v>
       </c>
       <c r="B6" s="9">
-        <f>MAX(0,MIN(B5,$B$37))*$C$37 + MAX(0,MIN(B5,$B$38)-$B$37)*$C$38 + MAX(0,MIN(B5,$B$39)-$B$38)*$C$10 + MAX(0,B5-$B$39)*$C$39</f>
+        <f t="shared" ref="B6:AU6" si="5">MAX(0,MIN(B5,$B$37))*$C$37 + MAX(0,MIN(B5,$B$38)-$B$37)*$C$38 + MAX(0,MIN(B5,$B$39)-$B$38)*$C$10 + MAX(0,B5-$B$39)*$C$39</f>
         <v>0</v>
       </c>
       <c r="C6" s="9">
-        <f>MAX(0,MIN(C5,$B$37))*$C$37 + MAX(0,MIN(C5,$B$38)-$B$37)*$C$38 + MAX(0,MIN(C5,$B$39)-$B$38)*$C$10 + MAX(0,C5-$B$39)*$C$39</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D6" s="9">
-        <f>MAX(0,MIN(D5,$B$37))*$C$37 + MAX(0,MIN(D5,$B$38)-$B$37)*$C$38 + MAX(0,MIN(D5,$B$39)-$B$38)*$C$10 + MAX(0,D5-$B$39)*$C$39</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="E6" s="9">
-        <f>MAX(0,MIN(E5,$B$37))*$C$37 + MAX(0,MIN(E5,$B$38)-$B$37)*$C$38 + MAX(0,MIN(E5,$B$39)-$B$38)*$C$10 + MAX(0,E5-$B$39)*$C$39</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F6" s="9">
-        <f>MAX(0,MIN(F5,$B$37))*$C$37 + MAX(0,MIN(F5,$B$38)-$B$37)*$C$38 + MAX(0,MIN(F5,$B$39)-$B$38)*$C$10 + MAX(0,F5-$B$39)*$C$39</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G6" s="9">
-        <f>MAX(0,MIN(G5,$B$37))*$C$37 + MAX(0,MIN(G5,$B$38)-$B$37)*$C$38 + MAX(0,MIN(G5,$B$39)-$B$38)*$C$10 + MAX(0,G5-$B$39)*$C$39</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H6" s="9">
-        <f>MAX(0,MIN(H5,$B$37))*$C$37 + MAX(0,MIN(H5,$B$38)-$B$37)*$C$38 + MAX(0,MIN(H5,$B$39)-$B$38)*$C$10 + MAX(0,H5-$B$39)*$C$39</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="I6" s="9">
-        <f>MAX(0,MIN(I5,$B$37))*$C$37 + MAX(0,MIN(I5,$B$38)-$B$37)*$C$38 + MAX(0,MIN(I5,$B$39)-$B$38)*$C$10 + MAX(0,I5-$B$39)*$C$39</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J6" s="9">
-        <f>MAX(0,MIN(J5,$B$37))*$C$37 + MAX(0,MIN(J5,$B$38)-$B$37)*$C$38 + MAX(0,MIN(J5,$B$39)-$B$38)*$C$10 + MAX(0,J5-$B$39)*$C$39</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="K6" s="9">
-        <f>MAX(0,MIN(K5,$B$37))*$C$37 + MAX(0,MIN(K5,$B$38)-$B$37)*$C$38 + MAX(0,MIN(K5,$B$39)-$B$38)*$C$10 + MAX(0,K5-$B$39)*$C$39</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="L6" s="9">
-        <f>MAX(0,MIN(L5,$B$37))*$C$37 + MAX(0,MIN(L5,$B$38)-$B$37)*$C$38 + MAX(0,MIN(L5,$B$39)-$B$38)*$C$10 + MAX(0,L5-$B$39)*$C$39</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="M6" s="9">
-        <f>MAX(0,MIN(M5,$B$37))*$C$37 + MAX(0,MIN(M5,$B$38)-$B$37)*$C$38 + MAX(0,MIN(M5,$B$39)-$B$38)*$C$10 + MAX(0,M5-$B$39)*$C$39</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N6" s="9">
-        <f>MAX(0,MIN(N5,$B$37))*$C$37 + MAX(0,MIN(N5,$B$38)-$B$37)*$C$38 + MAX(0,MIN(N5,$B$39)-$B$38)*$C$10 + MAX(0,N5-$B$39)*$C$39</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O6" s="9">
-        <f>MAX(0,MIN(O5,$B$37))*$C$37 + MAX(0,MIN(O5,$B$38)-$B$37)*$C$38 + MAX(0,MIN(O5,$B$39)-$B$38)*$C$10 + MAX(0,O5-$B$39)*$C$39</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="P6" s="9">
-        <f>MAX(0,MIN(P5,$B$37))*$C$37 + MAX(0,MIN(P5,$B$38)-$B$37)*$C$38 + MAX(0,MIN(P5,$B$39)-$B$38)*$C$10 + MAX(0,P5-$B$39)*$C$39</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q6" s="9">
-        <f>MAX(0,MIN(Q5,$B$37))*$C$37 + MAX(0,MIN(Q5,$B$38)-$B$37)*$C$38 + MAX(0,MIN(Q5,$B$39)-$B$38)*$C$10 + MAX(0,Q5-$B$39)*$C$39</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="R6" s="9">
-        <f>MAX(0,MIN(R5,$B$37))*$C$37 + MAX(0,MIN(R5,$B$38)-$B$37)*$C$38 + MAX(0,MIN(R5,$B$39)-$B$38)*$C$10 + MAX(0,R5-$B$39)*$C$39</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="S6" s="9">
-        <f>MAX(0,MIN(S5,$B$37))*$C$37 + MAX(0,MIN(S5,$B$38)-$B$37)*$C$38 + MAX(0,MIN(S5,$B$39)-$B$38)*$C$10 + MAX(0,S5-$B$39)*$C$39</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="T6" s="9">
-        <f>MAX(0,MIN(T5,$B$37))*$C$37 + MAX(0,MIN(T5,$B$38)-$B$37)*$C$38 + MAX(0,MIN(T5,$B$39)-$B$38)*$C$10 + MAX(0,T5-$B$39)*$C$39</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="U6" s="9">
-        <f>MAX(0,MIN(U5,$B$37))*$C$37 + MAX(0,MIN(U5,$B$38)-$B$37)*$C$38 + MAX(0,MIN(U5,$B$39)-$B$38)*$C$10 + MAX(0,U5-$B$39)*$C$39</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V6" s="9">
-        <f>MAX(0,MIN(V5,$B$37))*$C$37 + MAX(0,MIN(V5,$B$38)-$B$37)*$C$38 + MAX(0,MIN(V5,$B$39)-$B$38)*$C$10 + MAX(0,V5-$B$39)*$C$39</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W6" s="9">
-        <f>MAX(0,MIN(W5,$B$37))*$C$37 + MAX(0,MIN(W5,$B$38)-$B$37)*$C$38 + MAX(0,MIN(W5,$B$39)-$B$38)*$C$10 + MAX(0,W5-$B$39)*$C$39</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="X6" s="9">
-        <f>MAX(0,MIN(X5,$B$37))*$C$37 + MAX(0,MIN(X5,$B$38)-$B$37)*$C$38 + MAX(0,MIN(X5,$B$39)-$B$38)*$C$10 + MAX(0,X5-$B$39)*$C$39</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Y6" s="9">
-        <f>MAX(0,MIN(Y5,$B$37))*$C$37 + MAX(0,MIN(Y5,$B$38)-$B$37)*$C$38 + MAX(0,MIN(Y5,$B$39)-$B$38)*$C$10 + MAX(0,Y5-$B$39)*$C$39</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Z6" s="9">
-        <f>MAX(0,MIN(Z5,$B$37))*$C$37 + MAX(0,MIN(Z5,$B$38)-$B$37)*$C$38 + MAX(0,MIN(Z5,$B$39)-$B$38)*$C$10 + MAX(0,Z5-$B$39)*$C$39</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AA6" s="9">
-        <f>MAX(0,MIN(AA5,$B$37))*$C$37 + MAX(0,MIN(AA5,$B$38)-$B$37)*$C$38 + MAX(0,MIN(AA5,$B$39)-$B$38)*$C$10 + MAX(0,AA5-$B$39)*$C$39</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB6" s="9">
-        <f>MAX(0,MIN(AB5,$B$37))*$C$37 + MAX(0,MIN(AB5,$B$38)-$B$37)*$C$38 + MAX(0,MIN(AB5,$B$39)-$B$38)*$C$10 + MAX(0,AB5-$B$39)*$C$39</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AC6" s="9">
-        <f>MAX(0,MIN(AC5,$B$37))*$C$37 + MAX(0,MIN(AC5,$B$38)-$B$37)*$C$38 + MAX(0,MIN(AC5,$B$39)-$B$38)*$C$10 + MAX(0,AC5-$B$39)*$C$39</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AD6" s="9">
-        <f>MAX(0,MIN(AD5,$B$37))*$C$37 + MAX(0,MIN(AD5,$B$38)-$B$37)*$C$38 + MAX(0,MIN(AD5,$B$39)-$B$38)*$C$10 + MAX(0,AD5-$B$39)*$C$39</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AE6" s="9">
-        <f>MAX(0,MIN(AE5,$B$37))*$C$37 + MAX(0,MIN(AE5,$B$38)-$B$37)*$C$38 + MAX(0,MIN(AE5,$B$39)-$B$38)*$C$10 + MAX(0,AE5-$B$39)*$C$39</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AF6" s="9">
-        <f>MAX(0,MIN(AF5,$B$37))*$C$37 + MAX(0,MIN(AF5,$B$38)-$B$37)*$C$38 + MAX(0,MIN(AF5,$B$39)-$B$38)*$C$10 + MAX(0,AF5-$B$39)*$C$39</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AG6" s="9">
-        <f>MAX(0,MIN(AG5,$B$37))*$C$37 + MAX(0,MIN(AG5,$B$38)-$B$37)*$C$38 + MAX(0,MIN(AG5,$B$39)-$B$38)*$C$10 + MAX(0,AG5-$B$39)*$C$39</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AH6" s="9">
-        <f>MAX(0,MIN(AH5,$B$37))*$C$37 + MAX(0,MIN(AH5,$B$38)-$B$37)*$C$38 + MAX(0,MIN(AH5,$B$39)-$B$38)*$C$10 + MAX(0,AH5-$B$39)*$C$39</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AI6" s="9">
-        <f>MAX(0,MIN(AI5,$B$37))*$C$37 + MAX(0,MIN(AI5,$B$38)-$B$37)*$C$38 + MAX(0,MIN(AI5,$B$39)-$B$38)*$C$10 + MAX(0,AI5-$B$39)*$C$39</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AJ6" s="9">
-        <f>MAX(0,MIN(AJ5,$B$37))*$C$37 + MAX(0,MIN(AJ5,$B$38)-$B$37)*$C$38 + MAX(0,MIN(AJ5,$B$39)-$B$38)*$C$10 + MAX(0,AJ5-$B$39)*$C$39</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AK6" s="9">
-        <f>MAX(0,MIN(AK5,$B$37))*$C$37 + MAX(0,MIN(AK5,$B$38)-$B$37)*$C$38 + MAX(0,MIN(AK5,$B$39)-$B$38)*$C$10 + MAX(0,AK5-$B$39)*$C$39</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AL6" s="9">
-        <f>MAX(0,MIN(AL5,$B$37))*$C$37 + MAX(0,MIN(AL5,$B$38)-$B$37)*$C$38 + MAX(0,MIN(AL5,$B$39)-$B$38)*$C$10 + MAX(0,AL5-$B$39)*$C$39</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AM6" s="9">
-        <f>MAX(0,MIN(AM5,$B$37))*$C$37 + MAX(0,MIN(AM5,$B$38)-$B$37)*$C$38 + MAX(0,MIN(AM5,$B$39)-$B$38)*$C$10 + MAX(0,AM5-$B$39)*$C$39</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AN6" s="9">
-        <f>MAX(0,MIN(AN5,$B$37))*$C$37 + MAX(0,MIN(AN5,$B$38)-$B$37)*$C$38 + MAX(0,MIN(AN5,$B$39)-$B$38)*$C$10 + MAX(0,AN5-$B$39)*$C$39</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AO6" s="9">
-        <f>MAX(0,MIN(AO5,$B$37))*$C$37 + MAX(0,MIN(AO5,$B$38)-$B$37)*$C$38 + MAX(0,MIN(AO5,$B$39)-$B$38)*$C$10 + MAX(0,AO5-$B$39)*$C$39</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AP6" s="9">
-        <f>MAX(0,MIN(AP5,$B$37))*$C$37 + MAX(0,MIN(AP5,$B$38)-$B$37)*$C$38 + MAX(0,MIN(AP5,$B$39)-$B$38)*$C$10 + MAX(0,AP5-$B$39)*$C$39</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AQ6" s="9">
-        <f>MAX(0,MIN(AQ5,$B$37))*$C$37 + MAX(0,MIN(AQ5,$B$38)-$B$37)*$C$38 + MAX(0,MIN(AQ5,$B$39)-$B$38)*$C$10 + MAX(0,AQ5-$B$39)*$C$39</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AR6" s="9">
-        <f>MAX(0,MIN(AR5,$B$37))*$C$37 + MAX(0,MIN(AR5,$B$38)-$B$37)*$C$38 + MAX(0,MIN(AR5,$B$39)-$B$38)*$C$10 + MAX(0,AR5-$B$39)*$C$39</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AS6" s="9">
-        <f>MAX(0,MIN(AS5,$B$37))*$C$37 + MAX(0,MIN(AS5,$B$38)-$B$37)*$C$38 + MAX(0,MIN(AS5,$B$39)-$B$38)*$C$10 + MAX(0,AS5-$B$39)*$C$39</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AT6" s="9">
-        <f>MAX(0,MIN(AT5,$B$37))*$C$37 + MAX(0,MIN(AT5,$B$38)-$B$37)*$C$38 + MAX(0,MIN(AT5,$B$39)-$B$38)*$C$10 + MAX(0,AT5-$B$39)*$C$39</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AU6" s="9">
-        <f>MAX(0,MIN(AU5,$B$37))*$C$37 + MAX(0,MIN(AU5,$B$38)-$B$37)*$C$38 + MAX(0,MIN(AU5,$B$39)-$B$38)*$C$10 + MAX(0,AU5-$B$39)*$C$39</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:48" x14ac:dyDescent="0.3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
         <v>67</v>
       </c>
       <c r="B7" s="9">
-        <f t="shared" ref="B7:AU7" si="5">B4-B6</f>
+        <f t="shared" ref="B7:AU7" si="6">B4-B6</f>
         <v>0</v>
       </c>
       <c r="C7" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="D7" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E7" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="F7" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="G7" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H7" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="I7" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="J7" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="K7" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="L7" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="M7" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="N7" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O7" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="P7" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Q7" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R7" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="S7" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T7" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="U7" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="V7" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="W7" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="X7" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Y7" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Z7" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AA7" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AB7" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AC7" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD7" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE7" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AF7" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AG7" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AH7" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AI7" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AJ7" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AK7" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AL7" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AM7" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AN7" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AO7" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AP7" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AQ7" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AR7" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AS7" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AT7" s="9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AU7" s="9">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:48" x14ac:dyDescent="0.3">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
         <v>68</v>
       </c>
@@ -2340,385 +2340,385 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:48" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>1</v>
       </c>
       <c r="B9" s="9">
-        <f>IF($B$53="SI",B3/$B$43,0)</f>
+        <f t="shared" ref="B9:AU9" si="7">IF($B$53="SI",B3/$B$43,0)</f>
         <v>0</v>
       </c>
       <c r="C9" s="9">
-        <f>IF($B$53="SI",C3/$B$43,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="D9" s="9">
-        <f>IF($B$53="SI",D3/$B$43,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E9" s="9">
-        <f>IF($B$53="SI",E3/$B$43,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F9" s="9">
-        <f>IF($B$53="SI",F3/$B$43,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="G9" s="9">
-        <f>IF($B$53="SI",G3/$B$43,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H9" s="9">
-        <f>IF($B$53="SI",H3/$B$43,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I9" s="9">
-        <f>IF($B$53="SI",I3/$B$43,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J9" s="9">
-        <f>IF($B$53="SI",J3/$B$43,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="K9" s="9">
-        <f>IF($B$53="SI",K3/$B$43,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L9" s="9">
-        <f>IF($B$53="SI",L3/$B$43,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M9" s="9">
-        <f>IF($B$53="SI",M3/$B$43,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="N9" s="9">
-        <f>IF($B$53="SI",N3/$B$43,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="O9" s="9">
-        <f>IF($B$53="SI",O3/$B$43,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="P9" s="9">
-        <f>IF($B$53="SI",P3/$B$43,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Q9" s="9">
-        <f>IF($B$53="SI",Q3/$B$43,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="R9" s="9">
-        <f>IF($B$53="SI",R3/$B$43,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="S9" s="9">
-        <f>IF($B$53="SI",S3/$B$43,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T9" s="9">
-        <f>IF($B$53="SI",T3/$B$43,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="U9" s="9">
-        <f>IF($B$53="SI",U3/$B$43,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="V9" s="9">
-        <f>IF($B$53="SI",V3/$B$43,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="W9" s="9">
-        <f>IF($B$53="SI",W3/$B$43,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="X9" s="9">
-        <f>IF($B$53="SI",X3/$B$43,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Y9" s="9">
-        <f>IF($B$53="SI",Y3/$B$43,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Z9" s="9">
-        <f>IF($B$53="SI",Z3/$B$43,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AA9" s="9">
-        <f>IF($B$53="SI",AA3/$B$43,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AB9" s="9">
-        <f>IF($B$53="SI",AB3/$B$43,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AC9" s="9">
-        <f>IF($B$53="SI",AC3/$B$43,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AD9" s="9">
-        <f>IF($B$53="SI",AD3/$B$43,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AE9" s="9">
-        <f>IF($B$53="SI",AE3/$B$43,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AF9" s="9">
-        <f>IF($B$53="SI",AF3/$B$43,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AG9" s="9">
-        <f>IF($B$53="SI",AG3/$B$43,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AH9" s="9">
-        <f>IF($B$53="SI",AH3/$B$43,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AI9" s="9">
-        <f>IF($B$53="SI",AI3/$B$43,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AJ9" s="9">
-        <f>IF($B$53="SI",AJ3/$B$43,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AK9" s="9">
-        <f>IF($B$53="SI",AK3/$B$43,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AL9" s="9">
-        <f>IF($B$53="SI",AL3/$B$43,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AM9" s="9">
-        <f>IF($B$53="SI",AM3/$B$43,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AN9" s="9">
-        <f>IF($B$53="SI",AN3/$B$43,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AO9" s="9">
-        <f>IF($B$53="SI",AO3/$B$43,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AP9" s="9">
-        <f>IF($B$53="SI",AP3/$B$43,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AQ9" s="9">
-        <f>IF($B$53="SI",AQ3/$B$43,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AR9" s="9">
-        <f>IF($B$53="SI",AR3/$B$43,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AS9" s="9">
-        <f>IF($B$53="SI",AS3/$B$43,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AT9" s="9">
-        <f>IF($B$53="SI",AT3/$B$43,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="AU9" s="9">
-        <f>IF($B$53="SI",AU3/$B$43,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:48" x14ac:dyDescent="0.3">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
         <v>40</v>
       </c>
       <c r="B10" s="9">
-        <f>IF($B$54="SI",$B$47,0)</f>
+        <f t="shared" ref="B10:AU10" si="8">IF($B$54="SI",$B$47,0)</f>
         <v>0</v>
       </c>
       <c r="C10" s="9">
-        <f>IF($B$54="SI",$B$47,0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="D10" s="9">
-        <f>IF($B$54="SI",$B$47,0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E10" s="9">
-        <f>IF($B$54="SI",$B$47,0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="F10" s="9">
-        <f>IF($B$54="SI",$B$47,0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="G10" s="9">
-        <f>IF($B$54="SI",$B$47,0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H10" s="9">
-        <f>IF($B$54="SI",$B$47,0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="I10" s="9">
-        <f>IF($B$54="SI",$B$47,0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J10" s="9">
-        <f>IF($B$54="SI",$B$47,0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K10" s="9">
-        <f>IF($B$54="SI",$B$47,0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L10" s="9">
-        <f>IF($B$54="SI",$B$47,0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="M10" s="9">
-        <f>IF($B$54="SI",$B$47,0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="N10" s="9">
-        <f>IF($B$54="SI",$B$47,0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="O10" s="9">
-        <f>IF($B$54="SI",$B$47,0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="P10" s="9">
-        <f>IF($B$54="SI",$B$47,0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q10" s="9">
-        <f>IF($B$54="SI",$B$47,0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="R10" s="9">
-        <f>IF($B$54="SI",$B$47,0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="S10" s="9">
-        <f>IF($B$54="SI",$B$47,0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="T10" s="9">
-        <f>IF($B$54="SI",$B$47,0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U10" s="9">
-        <f>IF($B$54="SI",$B$47,0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="V10" s="9">
-        <f>IF($B$54="SI",$B$47,0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="W10" s="9">
-        <f>IF($B$54="SI",$B$47,0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="X10" s="9">
-        <f>IF($B$54="SI",$B$47,0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Y10" s="9">
-        <f>IF($B$54="SI",$B$47,0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Z10" s="9">
-        <f>IF($B$54="SI",$B$47,0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AA10" s="9">
-        <f>IF($B$54="SI",$B$47,0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AB10" s="9">
-        <f>IF($B$54="SI",$B$47,0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AC10" s="9">
-        <f>IF($B$54="SI",$B$47,0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AD10" s="9">
-        <f>IF($B$54="SI",$B$47,0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE10" s="9">
-        <f>IF($B$54="SI",$B$47,0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AF10" s="9">
-        <f>IF($B$54="SI",$B$47,0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AG10" s="9">
-        <f>IF($B$54="SI",$B$47,0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AH10" s="9">
-        <f>IF($B$54="SI",$B$47,0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AI10" s="9">
-        <f>IF($B$54="SI",$B$47,0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AJ10" s="9">
-        <f>IF($B$54="SI",$B$47,0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AK10" s="9">
-        <f>IF($B$54="SI",$B$47,0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AL10" s="9">
-        <f>IF($B$54="SI",$B$47,0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AM10" s="9">
-        <f>IF($B$54="SI",$B$47,0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AN10" s="9">
-        <f>IF($B$54="SI",$B$47,0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AO10" s="9">
-        <f>IF($B$54="SI",$B$47,0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AP10" s="9">
-        <f>IF($B$54="SI",$B$47,0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AQ10" s="9">
-        <f>IF($B$54="SI",$B$47,0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AR10" s="9">
-        <f>IF($B$54="SI",$B$47,0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AS10" s="9">
-        <f>IF($B$54="SI",$B$47,0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AT10" s="9">
-        <f>IF($B$54="SI",$B$47,0)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AU10" s="9">
-        <f>IF($B$54="SI",$B$47,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:48" x14ac:dyDescent="0.3">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
         <v>41</v>
       </c>
@@ -2907,7 +2907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:48" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>24</v>
       </c>
@@ -2916,187 +2916,187 @@
         <v>0</v>
       </c>
       <c r="C12" s="9">
-        <f t="shared" ref="C12:AU12" si="6">C11 - (C11*$B$40)</f>
+        <f t="shared" ref="C12:AU12" si="9">C11 - (C11*$B$40)</f>
         <v>0</v>
       </c>
       <c r="D12" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="E12" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F12" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="G12" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H12" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="I12" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="J12" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="K12" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L12" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="M12" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="N12" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="O12" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="P12" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Q12" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R12" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="S12" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="T12" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="U12" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="V12" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="W12" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="X12" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Y12" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Z12" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AA12" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AB12" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AC12" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AD12" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AE12" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AF12" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AG12" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AH12" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AI12" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AJ12" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AK12" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AL12" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AM12" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AN12" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AO12" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AP12" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AQ12" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AR12" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AS12" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AT12" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AU12" s="9">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:48" x14ac:dyDescent="0.3">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
         <v>42</v>
       </c>
@@ -3109,183 +3109,183 @@
         <v>0</v>
       </c>
       <c r="D13" s="9">
-        <f t="shared" ref="D13:AU13" si="7">IF(D12=0,0,D12/$C$49)</f>
+        <f t="shared" ref="D13:AU13" si="10">IF(D12=0,0,D12/$C$49)</f>
         <v>0</v>
       </c>
       <c r="E13" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="F13" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="G13" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="H13" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I13" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J13" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K13" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L13" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="M13" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="N13" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="O13" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="P13" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="Q13" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="R13" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="S13" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="T13" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U13" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="V13" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="W13" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="X13" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="Y13" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="Z13" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AA13" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AB13" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AC13" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AD13" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AE13" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AF13" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AG13" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AH13" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AI13" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AJ13" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AK13" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AL13" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AM13" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AN13" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AO13" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AP13" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AQ13" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AR13" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AS13" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AT13" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AU13" s="9">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:48" x14ac:dyDescent="0.3">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
         <v>10</v>
       </c>
@@ -3298,183 +3298,183 @@
         <v>0</v>
       </c>
       <c r="D14" s="9">
-        <f t="shared" ref="D14:AU14" si="8">IF(SUM(D9:D10)&gt;0,$B$52,0)</f>
+        <f t="shared" ref="D14:AU14" si="11">IF(SUM(D9:D10)&gt;0,$B$52,0)</f>
         <v>0</v>
       </c>
       <c r="E14" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="F14" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="G14" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="H14" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="I14" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J14" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K14" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L14" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="M14" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="N14" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="O14" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P14" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Q14" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="R14" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="S14" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="T14" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="U14" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="V14" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="W14" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="X14" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Y14" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Z14" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AA14" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AB14" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AC14" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AD14" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AE14" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AF14" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AG14" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AH14" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AI14" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AJ14" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK14" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AL14" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AM14" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AN14" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AO14" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AP14" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AQ14" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AR14" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AS14" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AT14" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AU14" s="9">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:48" x14ac:dyDescent="0.3">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>11</v>
       </c>
@@ -3663,7 +3663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:48" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A16" s="22"/>
       <c r="B16" s="22"/>
       <c r="C16" s="22"/>
@@ -3712,24 +3712,24 @@
       <c r="AT16" s="22"/>
       <c r="AU16" s="22"/>
     </row>
-    <row r="17" spans="1:47" x14ac:dyDescent="0.3">
-      <c r="A17" s="34" t="s">
+    <row r="17" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="A17" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="B17" s="35"/>
-      <c r="C17" s="36" t="s">
+      <c r="B17" s="43"/>
+      <c r="C17" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="D17" s="36"/>
-      <c r="E17" s="36"/>
-      <c r="F17" s="36"/>
-      <c r="G17" s="36"/>
-      <c r="H17" s="36"/>
-      <c r="I17" s="36"/>
-      <c r="J17" s="36"/>
-      <c r="K17" s="36"/>
-      <c r="L17" s="36"/>
-      <c r="M17" s="36"/>
+      <c r="D17" s="44"/>
+      <c r="E17" s="44"/>
+      <c r="F17" s="44"/>
+      <c r="G17" s="44"/>
+      <c r="H17" s="44"/>
+      <c r="I17" s="44"/>
+      <c r="J17" s="44"/>
+      <c r="K17" s="44"/>
+      <c r="L17" s="44"/>
+      <c r="M17" s="44"/>
       <c r="N17" s="22"/>
       <c r="O17" s="22"/>
       <c r="P17" s="22"/>
@@ -3765,7 +3765,7 @@
       <c r="AT17" s="22"/>
       <c r="AU17" s="22"/>
     </row>
-    <row r="18" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="s">
         <v>54</v>
       </c>
@@ -3773,19 +3773,19 @@
         <f>COUNT(B2:INDEX(2:2,MATCH(B46,1:1,0)))</f>
         <v>0</v>
       </c>
-      <c r="C18" s="31" t="s">
+      <c r="C18" s="39" t="s">
         <v>54</v>
       </c>
-      <c r="D18" s="31"/>
-      <c r="E18" s="31"/>
-      <c r="F18" s="31"/>
-      <c r="G18" s="31"/>
-      <c r="H18" s="31"/>
-      <c r="I18" s="31"/>
-      <c r="J18" s="31"/>
-      <c r="K18" s="31"/>
-      <c r="L18" s="31"/>
-      <c r="M18" s="31"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="39"/>
+      <c r="I18" s="39"/>
+      <c r="J18" s="39"/>
+      <c r="K18" s="39"/>
+      <c r="L18" s="39"/>
+      <c r="M18" s="39"/>
       <c r="N18" s="22"/>
       <c r="O18" s="22"/>
       <c r="P18" s="22"/>
@@ -3821,7 +3821,7 @@
       <c r="AT18" s="22"/>
       <c r="AU18" s="22"/>
     </row>
-    <row r="19" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="s">
         <v>36</v>
       </c>
@@ -3829,21 +3829,21 @@
         <f>IF(B55="SI",SUM(B9:INDEX(9:9,MATCH(B46,1:1,0))) + SUM(B10:INDEX(10:10,MATCH(B46,1:1,0))),0)</f>
         <v>0</v>
       </c>
-      <c r="C19" s="31" t="s">
+      <c r="C19" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="D19" s="31"/>
-      <c r="E19" s="31"/>
-      <c r="F19" s="31"/>
-      <c r="G19" s="31"/>
-      <c r="H19" s="31"/>
-      <c r="I19" s="31"/>
-      <c r="J19" s="31"/>
-      <c r="K19" s="31"/>
-      <c r="L19" s="31"/>
-      <c r="M19" s="31"/>
-    </row>
-    <row r="20" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="D19" s="39"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="39"/>
+      <c r="I19" s="39"/>
+      <c r="J19" s="39"/>
+      <c r="K19" s="39"/>
+      <c r="L19" s="39"/>
+      <c r="M19" s="39"/>
+    </row>
+    <row r="20" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
         <v>25</v>
       </c>
@@ -3851,21 +3851,21 @@
         <f>IF(B55="SI",SUM(B13:INDEX(13:13,MATCH(B46,1:1,0))),0)</f>
         <v>0</v>
       </c>
-      <c r="C20" s="31" t="s">
+      <c r="C20" s="39" t="s">
         <v>55</v>
       </c>
-      <c r="D20" s="31"/>
-      <c r="E20" s="31"/>
-      <c r="F20" s="31"/>
-      <c r="G20" s="31"/>
-      <c r="H20" s="31"/>
-      <c r="I20" s="31"/>
-      <c r="J20" s="31"/>
-      <c r="K20" s="31"/>
-      <c r="L20" s="31"/>
-      <c r="M20" s="31"/>
-    </row>
-    <row r="21" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="D20" s="39"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="39"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="39"/>
+      <c r="K20" s="39"/>
+      <c r="L20" s="39"/>
+      <c r="M20" s="39"/>
+    </row>
+    <row r="21" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>26</v>
       </c>
@@ -3873,21 +3873,21 @@
         <f>IF(B55="SI",B20/B19,0)</f>
         <v>0</v>
       </c>
-      <c r="C21" s="31" t="s">
+      <c r="C21" s="39" t="s">
         <v>55</v>
       </c>
-      <c r="D21" s="31"/>
-      <c r="E21" s="31"/>
-      <c r="F21" s="31"/>
-      <c r="G21" s="31"/>
-      <c r="H21" s="31"/>
-      <c r="I21" s="31"/>
-      <c r="J21" s="31"/>
-      <c r="K21" s="31"/>
-      <c r="L21" s="31"/>
-      <c r="M21" s="31"/>
-    </row>
-    <row r="22" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="D21" s="39"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="39"/>
+      <c r="I21" s="39"/>
+      <c r="J21" s="39"/>
+      <c r="K21" s="39"/>
+      <c r="L21" s="39"/>
+      <c r="M21" s="39"/>
+    </row>
+    <row r="22" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A22" s="18" t="s">
         <v>37</v>
       </c>
@@ -3895,21 +3895,21 @@
         <f>IF(B55="SI",SUM(B14:INDEX(14:14,MATCH(B46,1:1,0))) + SUM(B15:INDEX(15:15,MATCH(B46,1:1,0))),0)</f>
         <v>0</v>
       </c>
-      <c r="C22" s="31" t="s">
+      <c r="C22" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="D22" s="31"/>
-      <c r="E22" s="31"/>
-      <c r="F22" s="31"/>
-      <c r="G22" s="31"/>
-      <c r="H22" s="31"/>
-      <c r="I22" s="31"/>
-      <c r="J22" s="31"/>
-      <c r="K22" s="31"/>
-      <c r="L22" s="31"/>
-      <c r="M22" s="31"/>
-    </row>
-    <row r="23" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="D22" s="39"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="39"/>
+      <c r="H22" s="39"/>
+      <c r="I22" s="39"/>
+      <c r="J22" s="39"/>
+      <c r="K22" s="39"/>
+      <c r="L22" s="39"/>
+      <c r="M22" s="39"/>
+    </row>
+    <row r="23" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A23" s="18" t="s">
         <v>8</v>
       </c>
@@ -3917,21 +3917,21 @@
         <f>IF(B55="SI",B19*B42,0)</f>
         <v>0</v>
       </c>
-      <c r="C23" s="31" t="s">
+      <c r="C23" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="D23" s="31"/>
-      <c r="E23" s="31"/>
-      <c r="F23" s="31"/>
-      <c r="G23" s="31"/>
-      <c r="H23" s="31"/>
-      <c r="I23" s="31"/>
-      <c r="J23" s="31"/>
-      <c r="K23" s="31"/>
-      <c r="L23" s="31"/>
-      <c r="M23" s="31"/>
-    </row>
-    <row r="24" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="D23" s="39"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="39"/>
+      <c r="G23" s="39"/>
+      <c r="H23" s="39"/>
+      <c r="I23" s="39"/>
+      <c r="J23" s="39"/>
+      <c r="K23" s="39"/>
+      <c r="L23" s="39"/>
+      <c r="M23" s="39"/>
+    </row>
+    <row r="24" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
         <v>13</v>
       </c>
@@ -3939,21 +3939,21 @@
         <f>IF(B55="SI",B19+B20-B22-B23,0)</f>
         <v>0</v>
       </c>
-      <c r="C24" s="31" t="s">
+      <c r="C24" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="D24" s="31"/>
-      <c r="E24" s="31"/>
-      <c r="F24" s="31"/>
-      <c r="G24" s="31"/>
-      <c r="H24" s="31"/>
-      <c r="I24" s="31"/>
-      <c r="J24" s="31"/>
-      <c r="K24" s="31"/>
-      <c r="L24" s="31"/>
-      <c r="M24" s="31"/>
-    </row>
-    <row r="25" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="D24" s="39"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="39"/>
+      <c r="H24" s="39"/>
+      <c r="I24" s="39"/>
+      <c r="J24" s="39"/>
+      <c r="K24" s="39"/>
+      <c r="L24" s="39"/>
+      <c r="M24" s="39"/>
+    </row>
+    <row r="25" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A25" s="17" t="s">
         <v>27</v>
       </c>
@@ -3961,41 +3961,41 @@
         <f>IF(B55="SI",B24-B19,0)</f>
         <v>0</v>
       </c>
-      <c r="C25" s="31" t="s">
+      <c r="C25" s="39" t="s">
         <v>62</v>
       </c>
-      <c r="D25" s="31"/>
-      <c r="E25" s="31"/>
-      <c r="F25" s="31"/>
-      <c r="G25" s="31"/>
-      <c r="H25" s="31"/>
-      <c r="I25" s="31"/>
-      <c r="J25" s="31"/>
-      <c r="K25" s="31"/>
-      <c r="L25" s="31"/>
-      <c r="M25" s="31"/>
-    </row>
-    <row r="26" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="D25" s="39"/>
+      <c r="E25" s="39"/>
+      <c r="F25" s="39"/>
+      <c r="G25" s="39"/>
+      <c r="H25" s="39"/>
+      <c r="I25" s="39"/>
+      <c r="J25" s="39"/>
+      <c r="K25" s="39"/>
+      <c r="L25" s="39"/>
+      <c r="M25" s="39"/>
+    </row>
+    <row r="26" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A26" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="B26" s="38">
+      <c r="B26" s="32">
         <f>IF(B55="SI",B25/B19,0)</f>
         <v>0</v>
       </c>
-      <c r="C26" s="39"/>
-      <c r="D26" s="40"/>
-      <c r="E26" s="40"/>
-      <c r="F26" s="40"/>
-      <c r="G26" s="40"/>
-      <c r="H26" s="40"/>
-      <c r="I26" s="40"/>
-      <c r="J26" s="40"/>
-      <c r="K26" s="40"/>
-      <c r="L26" s="40"/>
-      <c r="M26" s="41"/>
-    </row>
-    <row r="27" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="C26" s="36"/>
+      <c r="D26" s="37"/>
+      <c r="E26" s="37"/>
+      <c r="F26" s="37"/>
+      <c r="G26" s="37"/>
+      <c r="H26" s="37"/>
+      <c r="I26" s="37"/>
+      <c r="J26" s="37"/>
+      <c r="K26" s="37"/>
+      <c r="L26" s="37"/>
+      <c r="M26" s="38"/>
+    </row>
+    <row r="27" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A27" s="17" t="s">
         <v>66</v>
       </c>
@@ -4003,21 +4003,21 @@
         <f>IF(B55="SI",SUM(B8:INDEX(8:8,MATCH(B46,1:1,0))),0)</f>
         <v>0</v>
       </c>
-      <c r="C27" s="31" t="s">
+      <c r="C27" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="D27" s="31"/>
-      <c r="E27" s="31"/>
-      <c r="F27" s="31"/>
-      <c r="G27" s="31"/>
-      <c r="H27" s="31"/>
-      <c r="I27" s="31"/>
-      <c r="J27" s="31"/>
-      <c r="K27" s="31"/>
-      <c r="L27" s="31"/>
-      <c r="M27" s="31"/>
-    </row>
-    <row r="28" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="D27" s="39"/>
+      <c r="E27" s="39"/>
+      <c r="F27" s="39"/>
+      <c r="G27" s="39"/>
+      <c r="H27" s="39"/>
+      <c r="I27" s="39"/>
+      <c r="J27" s="39"/>
+      <c r="K27" s="39"/>
+      <c r="L27" s="39"/>
+      <c r="M27" s="39"/>
+    </row>
+    <row r="28" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A28" s="26" t="s">
         <v>65</v>
       </c>
@@ -4025,21 +4025,21 @@
         <f>IF(B55="SI",(MAX(0,MIN(SUM(B9:INDEX(9:9,MATCH(B46,1:1,0)))+SUM(B10:INDEX(10:10,MATCH(B46,1:1,0))),$B$37))*$C$37+MAX(0,MIN(SUM(B9:INDEX(9:9,MATCH(B46,1:1,0)))+SUM(B10:INDEX(10:10,MATCH(B46,1:1,0))),$B$38)-$B$37)*$C$38+MAX(0,MIN(SUM(B9:INDEX(9:9,MATCH(B46,1:1,0)))+SUM(B10:INDEX(10:10,MATCH(B46,1:1,0))),$B$39)-$B$38)*$C$10+MAX(0,(SUM(B9:INDEX(9:9,MATCH(B46,1:1,0)))+SUM(B10:INDEX(10:10,MATCH(B46,1:1,0))))-$B$39)*$C$39),0)</f>
         <v>0</v>
       </c>
-      <c r="C28" s="31" t="s">
+      <c r="C28" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="D28" s="31"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="31"/>
-      <c r="I28" s="31"/>
-      <c r="J28" s="31"/>
-      <c r="K28" s="31"/>
-      <c r="L28" s="31"/>
-      <c r="M28" s="31"/>
-    </row>
-    <row r="29" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="D28" s="39"/>
+      <c r="E28" s="39"/>
+      <c r="F28" s="39"/>
+      <c r="G28" s="39"/>
+      <c r="H28" s="39"/>
+      <c r="I28" s="39"/>
+      <c r="J28" s="39"/>
+      <c r="K28" s="39"/>
+      <c r="L28" s="39"/>
+      <c r="M28" s="39"/>
+    </row>
+    <row r="29" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A29" s="26" t="s">
         <v>69</v>
       </c>
@@ -4059,7 +4059,7 @@
       <c r="L29" s="29"/>
       <c r="M29" s="29"/>
     </row>
-    <row r="30" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A30" s="17" t="s">
         <v>56</v>
       </c>
@@ -4067,21 +4067,21 @@
         <f>IF(B55="SI",SUM(B19:B20) / B44,0)</f>
         <v>0</v>
       </c>
-      <c r="C30" s="31" t="s">
+      <c r="C30" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="D30" s="31"/>
-      <c r="E30" s="31"/>
-      <c r="F30" s="31"/>
-      <c r="G30" s="31"/>
-      <c r="H30" s="31"/>
-      <c r="I30" s="31"/>
-      <c r="J30" s="31"/>
-      <c r="K30" s="31"/>
-      <c r="L30" s="31"/>
-      <c r="M30" s="31"/>
-    </row>
-    <row r="31" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="D30" s="39"/>
+      <c r="E30" s="39"/>
+      <c r="F30" s="39"/>
+      <c r="G30" s="39"/>
+      <c r="H30" s="39"/>
+      <c r="I30" s="39"/>
+      <c r="J30" s="39"/>
+      <c r="K30" s="39"/>
+      <c r="L30" s="39"/>
+      <c r="M30" s="39"/>
+    </row>
+    <row r="31" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
         <v>63</v>
       </c>
@@ -4089,21 +4089,21 @@
         <f>IF(B55="SI",B30/13,0)</f>
         <v>0</v>
       </c>
-      <c r="C31" s="31" t="s">
+      <c r="C31" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="D31" s="31"/>
-      <c r="E31" s="31"/>
-      <c r="F31" s="31"/>
-      <c r="G31" s="31"/>
-      <c r="H31" s="31"/>
-      <c r="I31" s="31"/>
-      <c r="J31" s="31"/>
-      <c r="K31" s="31"/>
-      <c r="L31" s="31"/>
-      <c r="M31" s="31"/>
-    </row>
-    <row r="32" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="D31" s="39"/>
+      <c r="E31" s="39"/>
+      <c r="F31" s="39"/>
+      <c r="G31" s="39"/>
+      <c r="H31" s="39"/>
+      <c r="I31" s="39"/>
+      <c r="J31" s="39"/>
+      <c r="K31" s="39"/>
+      <c r="L31" s="39"/>
+      <c r="M31" s="39"/>
+    </row>
+    <row r="32" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A32" s="17" t="s">
         <v>57</v>
       </c>
@@ -4111,7 +4111,7 @@
         <f>B24/B44</f>
         <v>0</v>
       </c>
-      <c r="C32" s="37"/>
+      <c r="C32" s="31"/>
       <c r="D32" s="30"/>
       <c r="E32" s="30"/>
       <c r="F32" s="30"/>
@@ -4123,7 +4123,7 @@
       <c r="L32" s="30"/>
       <c r="M32" s="30"/>
     </row>
-    <row r="33" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A33" s="17" t="s">
         <v>58</v>
       </c>
@@ -4143,7 +4143,7 @@
       <c r="L33" s="30"/>
       <c r="M33" s="30"/>
     </row>
-    <row r="34" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A34" s="22"/>
       <c r="B34" s="22"/>
       <c r="C34" s="22"/>
@@ -4192,20 +4192,20 @@
       <c r="AT34" s="22"/>
       <c r="AU34" s="22"/>
     </row>
-    <row r="35" spans="1:47" x14ac:dyDescent="0.3">
-      <c r="A35" s="32" t="s">
+    <row r="35" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="A35" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="B35" s="32"/>
-      <c r="C35" s="32"/>
+      <c r="B35" s="40"/>
+      <c r="C35" s="40"/>
       <c r="D35" s="1"/>
-      <c r="E35" s="33" t="s">
+      <c r="E35" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="F35" s="33"/>
-      <c r="G35" s="33"/>
-    </row>
-    <row r="36" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="F35" s="41"/>
+      <c r="G35" s="41"/>
+    </row>
+    <row r="36" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
         <v>17</v>
       </c>
@@ -4225,7 +4225,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
         <v>18</v>
       </c>
@@ -4248,7 +4248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A38" s="19" t="s">
         <v>19</v>
       </c>
@@ -4269,7 +4269,7 @@
         <v>0.43</v>
       </c>
     </row>
-    <row r="39" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A39" s="19" t="s">
         <v>20</v>
       </c>
@@ -4292,7 +4292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A40" s="19" t="s">
         <v>22</v>
       </c>
@@ -4308,7 +4308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A41" s="19" t="s">
         <v>43</v>
       </c>
@@ -4318,18 +4318,18 @@
       <c r="C41" s="3"/>
       <c r="G41" s="2"/>
     </row>
-    <row r="42" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A42" s="19" t="s">
         <v>45</v>
       </c>
       <c r="B42" s="8" t="e">
-        <f>15%-(0.3% * COUNTIFS(B2:INDEX(2:2,MATCH(B46,1:1,0)),"&lt;&gt;0"))</f>
+        <f>IF(15%-(0.3% * COUNTIFS(B2:INDEX(2:2,MATCH(B46,1:1,0)),"&lt;&gt;0"))&lt;9%,9%,15%-(0.3% * COUNTIFS(B2:INDEX(2:2,MATCH(B46,1:1,0)),"&lt;&gt;0")))</f>
         <v>#N/A</v>
       </c>
       <c r="C42" s="3"/>
       <c r="G42" s="2"/>
     </row>
-    <row r="43" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A43" s="19" t="s">
         <v>44</v>
       </c>
@@ -4339,7 +4339,7 @@
       <c r="C43" s="3"/>
       <c r="G43" s="2"/>
     </row>
-    <row r="44" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A44" s="19" t="s">
         <v>38</v>
       </c>
@@ -4348,29 +4348,29 @@
       </c>
       <c r="C44" s="3"/>
     </row>
-    <row r="45" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B45" s="42">
+      <c r="B45" s="33">
         <v>0</v>
       </c>
       <c r="C45" s="3"/>
     </row>
-    <row r="46" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A46" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B46" s="43">
+      <c r="B46" s="34">
         <v>0</v>
       </c>
       <c r="C46" s="3"/>
     </row>
-    <row r="47" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="B47" s="44">
+      <c r="B47" s="35">
         <v>5164.57</v>
       </c>
       <c r="C47" s="25">
@@ -4378,7 +4378,7 @@
         <v>430.38083333333333</v>
       </c>
     </row>
-    <row r="48" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
         <v>32</v>
       </c>
@@ -4387,7 +4387,7 @@
       </c>
       <c r="C48" s="3"/>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>31</v>
       </c>
@@ -4399,7 +4399,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
         <v>30</v>
       </c>
@@ -4408,7 +4408,7 @@
       </c>
       <c r="C50" s="3"/>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>12</v>
       </c>
@@ -4417,7 +4417,7 @@
       </c>
       <c r="C51" s="3"/>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="10" t="s">
         <v>39</v>
       </c>
@@ -4426,7 +4426,7 @@
       </c>
       <c r="C52" s="3"/>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>33</v>
       </c>
@@ -4435,7 +4435,7 @@
       </c>
       <c r="C53" s="3"/>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="10" t="s">
         <v>34</v>
       </c>
@@ -4444,7 +4444,7 @@
       </c>
       <c r="C54" s="3"/>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
         <v>35</v>
       </c>
@@ -4455,21 +4455,21 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="C21:M21"/>
+    <mergeCell ref="C22:M22"/>
+    <mergeCell ref="C23:M23"/>
+    <mergeCell ref="C24:M24"/>
+    <mergeCell ref="C25:M25"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:M17"/>
+    <mergeCell ref="C18:M18"/>
+    <mergeCell ref="C19:M19"/>
+    <mergeCell ref="C20:M20"/>
     <mergeCell ref="C26:M26"/>
     <mergeCell ref="C30:M30"/>
     <mergeCell ref="C31:M31"/>
     <mergeCell ref="A35:C35"/>
     <mergeCell ref="E35:G35"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:M17"/>
-    <mergeCell ref="C18:M18"/>
-    <mergeCell ref="C19:M19"/>
-    <mergeCell ref="C20:M20"/>
-    <mergeCell ref="C21:M21"/>
-    <mergeCell ref="C22:M22"/>
-    <mergeCell ref="C23:M23"/>
-    <mergeCell ref="C24:M24"/>
-    <mergeCell ref="C25:M25"/>
     <mergeCell ref="C27:M27"/>
     <mergeCell ref="C28:M28"/>
   </mergeCells>
